--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.88337175966769</v>
+        <v>-4.881328441091549</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.695967429204374</v>
+        <v>1.69678475663483</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6158087448980349</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.893756954557579</v>
+        <v>-4.891713635981438</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.701682130373491</v>
+        <v>1.702499457803947</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6054235500081456</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.912345113279804</v>
+        <v>-4.910301794703663</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.765083872661026</v>
+        <v>1.765901200091482</v>
       </c>
       <c r="F2038" t="n">
         <v>0.5868353912859203</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.91264365997584</v>
+        <v>-4.910600341399699</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.76183346480091</v>
+        <v>1.762650792231367</v>
       </c>
       <c r="F2039" t="n">
         <v>0.5865368445898844</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.811820526285413</v>
+        <v>-4.809777207709272</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.806693613216473</v>
+        <v>1.807510940646929</v>
       </c>
       <c r="F2040" t="n">
         <v>0.5990010600742383</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.621039165533006</v>
+        <v>-4.618995846956864</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.883135410995979</v>
+        <v>1.883952738426435</v>
       </c>
       <c r="F2041" t="n">
         <v>0.7897824208266456</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.602522311491185</v>
+        <v>-4.600478992915043</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.870378998350303</v>
+        <v>1.87119632578076</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8027125502518538</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.547191723589423</v>
+        <v>-4.545148405013281</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.927478170123067</v>
+        <v>1.928295497553524</v>
       </c>
       <c r="F2043" t="n">
         <v>0.858043138153616</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.53513759667646</v>
+        <v>-4.533094278100318</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.925986388789689</v>
+        <v>1.926803716220146</v>
       </c>
       <c r="F2044" t="n">
         <v>0.8700972650665788</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.576292716244681</v>
+        <v>-4.574249397668539</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.911404971146537</v>
+        <v>1.912222298576994</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8289421454983579</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.473412126716088</v>
+        <v>-4.471368808139946</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.965408232835856</v>
+        <v>1.966225560266313</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9318227350269508</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.705012519885589</v>
+        <v>-4.702969201309447</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.892970745741651</v>
+        <v>1.893788073172107</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9318227350269508</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.7230850281772</v>
+        <v>-4.721041709601058</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.885741742425006</v>
+        <v>1.886559069855463</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9318227350269508</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.898191860753645</v>
+        <v>-4.896148542177503</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.775950922987895</v>
+        <v>1.776768250418352</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9318227350269508</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.86690584021319</v>
+        <v>-4.864862521637048</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.795487950201017</v>
+        <v>1.796305277631474</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9631087555674062</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.713880448099905</v>
+        <v>-4.711837129523763</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.955869106619235</v>
+        <v>1.956686434049692</v>
       </c>
       <c r="F2051" t="n">
         <v>1.11613414768069</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.742187761973176</v>
+        <v>-4.740144443397034</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132012405978219</v>
+        <v>2.132829733408676</v>
       </c>
       <c r="F2052" t="n">
         <v>1.11613414768069</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.908780987086698</v>
+        <v>-4.906737668510556</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.034778067286893</v>
+        <v>2.035595394717349</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9495409225671678</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.735716607704398</v>
+        <v>-4.733673289128256</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.10768022170153</v>
+        <v>2.108497549131987</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9495409225671678</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.706470627248701</v>
+        <v>-4.704427308672559</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.116996669007304</v>
+        <v>2.117813996437761</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9495409225671678</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.813396175126552</v>
+        <v>-4.81135285655041</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.071519689013798</v>
+        <v>2.072337016444255</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8426153746893165</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.958414733633801</v>
+        <v>-4.956371415057659</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.014941067754133</v>
+        <v>2.01575839518459</v>
       </c>
       <c r="F2057" t="n">
         <v>0.6975968161820679</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.076756499418519</v>
+        <v>-5.074713180842377</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.067535600697999</v>
+        <v>2.068352928128456</v>
       </c>
       <c r="F2058" t="n">
         <v>0.708282854744958</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.128166921739227</v>
+        <v>-5.126123603163085</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.044757128895655</v>
+        <v>2.045574456326112</v>
       </c>
       <c r="F2059" t="n">
         <v>0.708282854744958</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.207586372946978</v>
+        <v>-5.205543054370836</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.012892476486844</v>
+        <v>2.013709803917301</v>
       </c>
       <c r="F2060" t="n">
         <v>0.708282854744958</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581132</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.303049370864196</v>
+        <v>-5.301006052288054</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.974701170878</v>
+        <v>1.975518498308457</v>
       </c>
       <c r="F2061" t="n">
         <v>0.708282854744958</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500734</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.34306936890798</v>
+        <v>-5.341026050331838</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.956789568223097</v>
+        <v>1.957606895653554</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6682628567011741</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636269</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.398438531040173</v>
+        <v>-5.396395212464031</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.940375721117947</v>
+        <v>1.941193048548403</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6682628567011741</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.443876310871</v>
+        <v>-5.441832992294859</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.921738972528548</v>
+        <v>1.922556299959005</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6254178660230145</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.360650854023336</v>
+        <v>-5.358607535447194</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.974903548117933</v>
+        <v>1.97572087554839</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6254178660230145</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.184360629418029</v>
+        <v>-5.182317310841887</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.029120338484784</v>
+        <v>2.029937665915241</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6254178660230145</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.001148966284934</v>
+        <v>-4.999105647708792</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.104835953202068</v>
+        <v>2.105653280632525</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6254178660230145</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.929427519271083</v>
+        <v>-4.927384200694941</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.099315717855498</v>
+        <v>2.100133045285954</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6971393130368652</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.05880630191086</v>
+        <v>-5.056762983334719</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.994479950720758</v>
+        <v>1.995297278151215</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6550375403296618</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.091822597821605</v>
+        <v>-5.089779279245463</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.166471637241816</v>
+        <v>2.167288964672272</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5856001636629102</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.080294962171997</v>
+        <v>-5.078251643595855</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.163003917329908</v>
+        <v>2.163821244760365</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6446008218642727</v>
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.842120064624739</v>
+        <v>3.842120064624737</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.264066345598597</v>
+        <v>-5.263903677986208</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.093163476481056</v>
+        <v>2.093228543526012</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5679702953805676</v>
+        <v>0.5678056323654554</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.539928616262584</v>
+        <v>4.539829818453516</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.0%</t>
+          <t>-679.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.8%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-164.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.842120064624737</v>
+        <v>3.842120064624739</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.263903677986208</v>
+        <v>-5.175593144938223</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.093228543526012</v>
+        <v>2.128552756745206</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5678056323654554</v>
+        <v>0.6001806396987843</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.539829818453516</v>
+        <v>4.559254822853513</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.1%</t>
+          <t>-688.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-166.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.9%</t>
+          <t>590.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.5%</t>
+          <t>-308.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -48379,10 +48379,10 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.881328441091549</v>
+        <v>-4.969917741581726</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.69678475663483</v>
+        <v>1.66134903643876</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6158087448980349</v>
@@ -48402,10 +48402,10 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.891713635981438</v>
+        <v>-4.980302936471615</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.702499457803947</v>
+        <v>1.667063737607877</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6054235500081456</v>
@@ -48425,10 +48425,10 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.910301794703663</v>
+        <v>-4.99889109519384</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.765901200091482</v>
+        <v>1.730465479895412</v>
       </c>
       <c r="F2038" t="n">
         <v>0.5868353912859203</v>
@@ -48448,10 +48448,10 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.910600341399699</v>
+        <v>-4.999189641889876</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.762650792231367</v>
+        <v>1.727215072035296</v>
       </c>
       <c r="F2039" t="n">
         <v>0.5865368445898844</v>
@@ -48471,10 +48471,10 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.809777207709272</v>
+        <v>-4.898366508199448</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.807510940646929</v>
+        <v>1.772075220450858</v>
       </c>
       <c r="F2040" t="n">
         <v>0.5990010600742383</v>
@@ -48494,10 +48494,10 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.618995846956864</v>
+        <v>-4.707585147447041</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.883952738426435</v>
+        <v>1.848517018230365</v>
       </c>
       <c r="F2041" t="n">
         <v>0.7897824208266456</v>
@@ -48517,10 +48517,10 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.600478992915043</v>
+        <v>-4.689068293405221</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.87119632578076</v>
+        <v>1.835760605584689</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8027125502518538</v>
@@ -48540,10 +48540,10 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545148405013281</v>
+        <v>-4.633737705503458</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928295497553524</v>
+        <v>1.892859777357452</v>
       </c>
       <c r="F2043" t="n">
         <v>0.858043138153616</v>
@@ -48563,10 +48563,10 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.533094278100318</v>
+        <v>-4.621683578590496</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926803716220146</v>
+        <v>1.891367996024075</v>
       </c>
       <c r="F2044" t="n">
         <v>0.8700972650665788</v>
@@ -48586,10 +48586,10 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574249397668539</v>
+        <v>-4.662838698158716</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912222298576994</v>
+        <v>1.876786578380923</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8289421454983579</v>
@@ -48609,10 +48609,10 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.471368808139946</v>
+        <v>-4.559958108630124</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.966225560266313</v>
+        <v>1.930789840070243</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9318227350269508</v>
@@ -48632,10 +48632,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.702969201309447</v>
+        <v>-4.791558501799624</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.893788073172107</v>
+        <v>1.858352352976036</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9318227350269508</v>
@@ -48655,10 +48655,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721041709601058</v>
+        <v>-4.809631010091236</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886559069855463</v>
+        <v>1.851123349659392</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9318227350269508</v>
@@ -48678,10 +48678,10 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.896148542177503</v>
+        <v>-4.98473784266768</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776768250418352</v>
+        <v>1.741332530222281</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9318227350269508</v>
@@ -48701,10 +48701,10 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.864862521637048</v>
+        <v>-4.953451822127225</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.796305277631474</v>
+        <v>1.760869557435403</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9631087555674062</v>
@@ -48724,10 +48724,10 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.711837129523763</v>
+        <v>-4.800426430013941</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.956686434049692</v>
+        <v>1.921250713853621</v>
       </c>
       <c r="F2051" t="n">
         <v>1.11613414768069</v>
@@ -48747,10 +48747,10 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.740144443397034</v>
+        <v>-4.828733743887211</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132829733408676</v>
+        <v>2.097394013212605</v>
       </c>
       <c r="F2052" t="n">
         <v>1.11613414768069</v>
@@ -48770,10 +48770,10 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.906737668510556</v>
+        <v>-4.995326969000733</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.035595394717349</v>
+        <v>2.000159674521278</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9495409225671678</v>
@@ -48793,10 +48793,10 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.733673289128256</v>
+        <v>-4.822262589618433</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.108497549131987</v>
+        <v>2.073061828935916</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9495409225671678</v>
@@ -48816,10 +48816,10 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.704427308672559</v>
+        <v>-4.793016609162737</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.117813996437761</v>
+        <v>2.08237827624169</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9495409225671678</v>
@@ -48839,10 +48839,10 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.81135285655041</v>
+        <v>-4.899942157040588</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.072337016444255</v>
+        <v>2.036901296248185</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8426153746893165</v>
@@ -48862,10 +48862,10 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.956371415057659</v>
+        <v>-5.044960715547837</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.01575839518459</v>
+        <v>1.980322674988519</v>
       </c>
       <c r="F2057" t="n">
         <v>0.6975968161820679</v>
@@ -48885,10 +48885,10 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.074713180842377</v>
+        <v>-5.163302481332554</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068352928128456</v>
+        <v>2.032917207932385</v>
       </c>
       <c r="F2058" t="n">
         <v>0.708282854744958</v>
@@ -48908,10 +48908,10 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.126123603163085</v>
+        <v>-5.214712903653262</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.045574456326112</v>
+        <v>2.01013873613004</v>
       </c>
       <c r="F2059" t="n">
         <v>0.708282854744958</v>
@@ -48931,10 +48931,10 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.205543054370836</v>
+        <v>-5.294132354861014</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.013709803917301</v>
+        <v>1.978274083721229</v>
       </c>
       <c r="F2060" t="n">
         <v>0.708282854744958</v>
@@ -48954,10 +48954,10 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.301006052288054</v>
+        <v>-5.389595352778231</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.975518498308457</v>
+        <v>1.940082778112386</v>
       </c>
       <c r="F2061" t="n">
         <v>0.708282854744958</v>
@@ -48977,10 +48977,10 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.341026050331838</v>
+        <v>-5.429615350822015</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957606895653554</v>
+        <v>1.922171175457483</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6682628567011741</v>
@@ -49000,10 +49000,10 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.396395212464031</v>
+        <v>-5.484984512954209</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941193048548403</v>
+        <v>1.905757328352332</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6682628567011741</v>
@@ -49023,10 +49023,10 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.441832992294859</v>
+        <v>-5.530422292785036</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.922556299959005</v>
+        <v>1.887120579762934</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6254178660230145</v>
@@ -49046,10 +49046,10 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.358607535447194</v>
+        <v>-5.447196835937372</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.97572087554839</v>
+        <v>1.940285155352319</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6254178660230145</v>
@@ -49069,10 +49069,10 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.182317310841887</v>
+        <v>-5.270906611332064</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.029937665915241</v>
+        <v>1.99450194571917</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6254178660230145</v>
@@ -49092,10 +49092,10 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.999105647708792</v>
+        <v>-5.087694948198969</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.105653280632525</v>
+        <v>2.070217560436454</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6254178660230145</v>
@@ -49115,10 +49115,10 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.927384200694941</v>
+        <v>-5.015973501185118</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.100133045285954</v>
+        <v>2.064697325089883</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6971393130368652</v>
@@ -49138,10 +49138,10 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.056762983334719</v>
+        <v>-5.145352283824896</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.995297278151215</v>
+        <v>1.959861557955144</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6550375403296618</v>
@@ -49161,10 +49161,10 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.089779279245463</v>
+        <v>-5.178368579735641</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.167288964672272</v>
+        <v>2.131853244476202</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5856001636629102</v>
@@ -49184,10 +49184,10 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.078251643595855</v>
+        <v>-5.166840944086032</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.163821244760365</v>
+        <v>2.128385524564294</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6446008218642727</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.842120064624739</v>
+        <v>3.746894932493014</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.175593144938223</v>
+        <v>-5.264182445428401</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.128552756745206</v>
+        <v>2.093117036549135</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6001806396987843</v>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>125.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>423.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.0%</t>
+          <t>-679.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.5%</t>
+          <t>590.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.4%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2072"/>
+  <dimension ref="A1:G2073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
@@ -48379,10 +48379,10 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.969917741581726</v>
+        <v>-4.881328441091549</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66134903643876</v>
+        <v>1.69678475663483</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6158087448980349</v>
@@ -48402,10 +48402,10 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.980302936471615</v>
+        <v>-4.891713635981438</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.667063737607877</v>
+        <v>1.702499457803947</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6054235500081456</v>
@@ -48425,10 +48425,10 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.99889109519384</v>
+        <v>-4.910301794703663</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.730465479895412</v>
+        <v>1.765901200091482</v>
       </c>
       <c r="F2038" t="n">
         <v>0.5868353912859203</v>
@@ -48448,10 +48448,10 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.999189641889876</v>
+        <v>-4.910600341399699</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.727215072035296</v>
+        <v>1.762650792231367</v>
       </c>
       <c r="F2039" t="n">
         <v>0.5865368445898844</v>
@@ -48471,10 +48471,10 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.898366508199448</v>
+        <v>-4.809777207709272</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.772075220450858</v>
+        <v>1.807510940646929</v>
       </c>
       <c r="F2040" t="n">
         <v>0.5990010600742383</v>
@@ -48494,10 +48494,10 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.707585147447041</v>
+        <v>-4.618995846956864</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.848517018230365</v>
+        <v>1.883952738426435</v>
       </c>
       <c r="F2041" t="n">
         <v>0.7897824208266456</v>
@@ -48517,10 +48517,10 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.689068293405221</v>
+        <v>-4.600478992915043</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.835760605584689</v>
+        <v>1.87119632578076</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8027125502518538</v>
@@ -48540,10 +48540,10 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.633737705503458</v>
+        <v>-4.545148405013281</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.892859777357452</v>
+        <v>1.928295497553524</v>
       </c>
       <c r="F2043" t="n">
         <v>0.858043138153616</v>
@@ -48563,10 +48563,10 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.621683578590496</v>
+        <v>-4.533094278100318</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.891367996024075</v>
+        <v>1.926803716220146</v>
       </c>
       <c r="F2044" t="n">
         <v>0.8700972650665788</v>
@@ -48586,10 +48586,10 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.662838698158716</v>
+        <v>-4.574249397668539</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.876786578380923</v>
+        <v>1.912222298576994</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8289421454983579</v>
@@ -48609,10 +48609,10 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.559958108630124</v>
+        <v>-4.471368808139946</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.930789840070243</v>
+        <v>1.966225560266313</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9318227350269508</v>
@@ -48632,10 +48632,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.791558501799624</v>
+        <v>-4.702969201309447</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.858352352976036</v>
+        <v>1.893788073172107</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9318227350269508</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.809631010091236</v>
+        <v>-4.721041709601058</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.851123349659392</v>
+        <v>1.886559069855463</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9318227350269508</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.98473784266768</v>
+        <v>-4.896148542177503</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.741332530222281</v>
+        <v>1.776768250418352</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9318227350269508</v>
@@ -48701,10 +48701,10 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.953451822127225</v>
+        <v>-4.864862521637048</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.760869557435403</v>
+        <v>1.796305277631474</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9631087555674062</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.800426430013941</v>
+        <v>-4.711837129523763</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.921250713853621</v>
+        <v>1.956686434049692</v>
       </c>
       <c r="F2051" t="n">
         <v>1.11613414768069</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.828733743887211</v>
+        <v>-4.740144443397034</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.097394013212605</v>
+        <v>2.132829733408676</v>
       </c>
       <c r="F2052" t="n">
         <v>1.11613414768069</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.995326969000733</v>
+        <v>-4.906737668510556</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.000159674521278</v>
+        <v>2.035595394717349</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9495409225671678</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.822262589618433</v>
+        <v>-4.733673289128256</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.073061828935916</v>
+        <v>2.108497549131987</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9495409225671678</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.793016609162737</v>
+        <v>-4.704427308672559</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.08237827624169</v>
+        <v>2.117813996437761</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9495409225671678</v>
@@ -48839,10 +48839,10 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.899942157040588</v>
+        <v>-4.81135285655041</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.036901296248185</v>
+        <v>2.072337016444255</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8426153746893165</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.044960715547837</v>
+        <v>-4.956371415057659</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.980322674988519</v>
+        <v>2.01575839518459</v>
       </c>
       <c r="F2057" t="n">
         <v>0.6975968161820679</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.163302481332554</v>
+        <v>-5.074713180842377</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.032917207932385</v>
+        <v>2.068352928128456</v>
       </c>
       <c r="F2058" t="n">
         <v>0.708282854744958</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073536</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.214712903653262</v>
+        <v>-5.126123603163085</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.01013873613004</v>
+        <v>2.045574456326112</v>
       </c>
       <c r="F2059" t="n">
         <v>0.708282854744958</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.294132354861014</v>
+        <v>-5.205543054370836</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.978274083721229</v>
+        <v>2.013709803917301</v>
       </c>
       <c r="F2060" t="n">
         <v>0.708282854744958</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.389595352778231</v>
+        <v>-5.301006052288054</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.940082778112386</v>
+        <v>1.975518498308457</v>
       </c>
       <c r="F2061" t="n">
         <v>0.708282854744958</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.429615350822015</v>
+        <v>-5.341026050331838</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.922171175457483</v>
+        <v>1.957606895653554</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6682628567011741</v>
@@ -49000,10 +49000,10 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.484984512954209</v>
+        <v>-5.396395212464031</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.905757328352332</v>
+        <v>1.941193048548403</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6682628567011741</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.530422292785036</v>
+        <v>-5.441832992294859</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.887120579762934</v>
+        <v>1.922556299959005</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6254178660230145</v>
@@ -49046,10 +49046,10 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.447196835937372</v>
+        <v>-5.358607535447194</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.940285155352319</v>
+        <v>1.97572087554839</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6254178660230145</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.270906611332064</v>
+        <v>-5.182317310841887</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.99450194571917</v>
+        <v>2.029937665915241</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6254178660230145</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.087694948198969</v>
+        <v>-4.999105647708792</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.070217560436454</v>
+        <v>2.105653280632525</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6254178660230145</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.015973501185118</v>
+        <v>-4.927384200694941</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.064697325089883</v>
+        <v>2.100133045285954</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6971393130368652</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.145352283824896</v>
+        <v>-5.056762983334719</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.959861557955144</v>
+        <v>1.995297278151215</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6550375403296618</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.178368579735641</v>
+        <v>-5.089779279245463</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.131853244476202</v>
+        <v>2.167288964672272</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5856001636629102</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.166840944086032</v>
+        <v>-5.078251643595855</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.128385524564294</v>
+        <v>2.163821244760365</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6446008218642727</v>
@@ -49201,22 +49201,45 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.746894932493014</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.264182445428401</v>
+        <v>-5.175593144938223</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.093117036549135</v>
+        <v>2.128552756745206</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6001806396987843</v>
       </c>
       <c r="G2072" t="n">
         <v>4.559254822853513</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="2" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>3.841698146045359</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>4.374725299244116</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>-5.175593144938223</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>2.128552756745206</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>0.6001806396987843</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>4.367789096230484</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>124.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.1%</t>
+          <t>-672.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-160.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.5%</t>
+          <t>-307.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.0%</t>
+          <t>-157.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.341026050331838</v>
+        <v>-5.278256820353828</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957606895653554</v>
+        <v>1.982714587644758</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6682628567011741</v>
+        <v>0.731032086679184</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.495331454120741</v>
+        <v>4.532992992107547</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.396395212464031</v>
+        <v>-5.333625982486022</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941193048548403</v>
+        <v>1.966300740539607</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6682628567011741</v>
+        <v>0.731032086679184</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.501065271868468</v>
+        <v>4.538726809855274</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.441832992294859</v>
+        <v>-5.379063762316849</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.922556299959005</v>
+        <v>1.947663991950209</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6254178660230145</v>
+        <v>0.6881870960010243</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.474896640804505</v>
+        <v>4.512558178791311</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79029268539642</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.358607535447194</v>
+        <v>-5.295838305469185</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.97572087554839</v>
+        <v>2.000828567539594</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6254178660230145</v>
+        <v>0.6881870960010243</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.494771033654824</v>
+        <v>4.53243257164163</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.182317310841887</v>
+        <v>-5.119548080863877</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.029937665915241</v>
+        <v>2.055045357906445</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6254178660230145</v>
+        <v>0.6881870960010243</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.478471734179552</v>
+        <v>4.516133272166358</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.999105647708792</v>
+        <v>-4.936336417730782</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.105653280632525</v>
+        <v>2.130760972623728</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6254178660230145</v>
+        <v>0.6881870960010243</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.480902683643597</v>
+        <v>4.518564221630403</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.927384200694941</v>
+        <v>-4.864614970716931</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.100133045285954</v>
+        <v>2.125240737277158</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6971393130368652</v>
+        <v>0.759908543014875</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.489726737699797</v>
+        <v>4.527388275686603</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.056762983334719</v>
+        <v>-4.993993753356709</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.995297278151215</v>
+        <v>2.020404970142418</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6550375403296618</v>
+        <v>0.7178067703076716</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.411381419996647</v>
+        <v>4.449042957983453</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.089779279245463</v>
+        <v>-5.027010049267454</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.167288964672272</v>
+        <v>2.192396656663476</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5856001636629102</v>
+        <v>0.6483693936409201</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.554917198881951</v>
+        <v>4.592578736868758</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.078251643595855</v>
+        <v>-5.015482413617845</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.163821244760365</v>
+        <v>2.188928936751569</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6446008218642727</v>
+        <v>0.7073700518422825</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.582238819631018</v>
+        <v>4.619900357617824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.175593144938223</v>
+        <v>-5.112823914960214</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.128552756745206</v>
+        <v>2.15366044873641</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6001806396987843</v>
+        <v>0.6629498696767941</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.559254822853513</v>
+        <v>4.59691636084032</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.841698146045359</v>
+        <v>3.815293335538338</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.374725299244116</v>
+        <v>4.364439701821476</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.175593144938223</v>
+        <v>-5.112823914960214</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.128552756745206</v>
+        <v>2.15366044873641</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6001806396987843</v>
+        <v>0.6629498696767941</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.367789096230484</v>
+        <v>4.357503498807843</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>120.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>422.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.9%</t>
+          <t>-683.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-165.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.9%</t>
+          <t>590.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.7%</t>
+          <t>-152.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-15.0%</t>
         </is>
       </c>
     </row>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.676715012510379</v>
+        <v>-3.648318729253103</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.904989592314158</v>
+        <v>1.916348105617068</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.7878839615667601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.848762398572113</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.704615799619852</v>
+        <v>-3.676219516362576</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.892353318597371</v>
+        <v>1.903711831900281</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.7532870374238253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.826528285213354</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.827141902322746</v>
+        <v>-3.79874561906547</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.840107321493412</v>
+        <v>1.851465834796322</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.6307609347209314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.749777067568816</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.057656398508334</v>
+        <v>-4.029260115251059</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.81460748260968</v>
+        <v>1.82596599591259</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.4002464385353427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.678174329447967</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.406401483732778</v>
+        <v>-4.378005200475503</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.81542116752175</v>
+        <v>1.82677968082466</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2914984846164449</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.753237276098475</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.560387901508919</v>
+        <v>-4.531991618251643</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.822806869556933</v>
+        <v>1.834165382859843</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2914984846164449</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.822217545244115</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.509865997681253</v>
+        <v>-4.481469714423977</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.82906683320812</v>
+        <v>1.840425346511031</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2914984846164449</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.808268747364236</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.762341151688977</v>
+        <v>-4.733944868431702</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.739947260660445</v>
+        <v>1.751305773963355</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2914984846164449</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.82013923641965</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.055236908168389</v>
+        <v>-5.026840624911114</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.623999492587624</v>
+        <v>1.635358005890533</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2914984846164449</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.821349770938594</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.241901036303197</v>
+        <v>-5.213504753045922</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.553455583561022</v>
+        <v>1.564814096863932</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.264759513791885</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.809428130671179</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.387921723217159</v>
+        <v>-5.359525439959884</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.490125161531626</v>
+        <v>1.501483674834536</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.255676421998028</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.799056128331054</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.479635732326745</v>
+        <v>-5.451239449069469</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.615643614586836</v>
+        <v>1.627002127889746</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.255676421998028</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>3.961260185030098</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.511287391386714</v>
+        <v>-5.482891108129438</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.597829588926662</v>
+        <v>1.609188102229573</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.2505079647535878</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>3.953005748647248</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.593222209655598</v>
+        <v>-5.564825926398322</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.575285079187601</v>
+        <v>1.586643592490511</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.2405732191665076</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>3.957274318863491</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.695198331904005</v>
+        <v>-5.666802048646729</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.54342026874414</v>
+        <v>1.55477878204705</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.1385970969181001</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.905014283970349</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.585192048426784</v>
+        <v>-5.556795765169507</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.579575669379204</v>
+        <v>1.590934182682114</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.1618016688353753</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.91108991436489</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.442132472685858</v>
+        <v>-5.458474222443379</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.641049510397548</v>
+        <v>1.63451281049454</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.1974199902319372</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.936710917924802</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.14068574721402</v>
+        <v>-5.157027496971542</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.76888908346882</v>
+        <v>1.762352383565811</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4988667157037745</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>4.12483983609044</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.165275991449204</v>
+        <v>-5.181617741206725</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.760024163527456</v>
+        <v>1.753487463624448</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4988667157037745</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>4.12581101384315</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.114237615442684</v>
+        <v>-5.130579365200205</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.78128241830982</v>
+        <v>1.774745718406812</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4988667157037745</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>4.126653918222906</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.073098320576053</v>
+        <v>-5.089440070333574</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.816776235130618</v>
+        <v>1.810239535227609</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.5400060105704053</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.17037559401703</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.976463408557413</v>
+        <v>-4.992805158314934</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.671614196062009</v>
+        <v>1.665077496159</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.6366409225890453</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>4.044540537352148</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.107044143088255</v>
+        <v>-5.123385892845777</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.622883946323636</v>
+        <v>1.616347246420627</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.5060601880582027</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>3.969694140707607</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.942547808897293</v>
+        <v>-4.958889558654815</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.673109299076103</v>
+        <v>1.666572599173094</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6705565222491646</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>4.052818760298266</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.881328441091549</v>
+        <v>-4.986259491339247</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.69678475663483</v>
+        <v>1.654812336535751</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6705565222491646</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>4.052006470734696</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.891713635981438</v>
+        <v>-4.996644686229136</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.702499457803947</v>
+        <v>1.660527037704868</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.6601713273592753</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>4.055644132925835</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.910301794703663</v>
+        <v>-5.015232844951361</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.765901200091482</v>
+        <v>1.723928779992403</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.6415831686370499</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>4.115328243468925</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.910600341399699</v>
+        <v>-5.015531391647397</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.762650792231367</v>
+        <v>1.720678372132287</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.641284621941014</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>4.112018126269602</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.809777207709272</v>
+        <v>-4.91470825795697</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.807510940646929</v>
+        <v>1.76553852054785</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.6537488374253678</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>4.124027550499606</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.618995846956864</v>
+        <v>-4.723926897204562</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.883952738426435</v>
+        <v>1.841980318327356</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.8445301981777752</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.238625620429594</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.600478992915043</v>
+        <v>-4.705410043162741</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.87119632578076</v>
+        <v>1.829223905681681</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8027125502518538</v>
+        <v>0.8574603276029834</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.193371877411638</v>
+        <v>4.226220543822315</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545148405013281</v>
+        <v>-4.650079455260979</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928295497553524</v>
+        <v>1.886323077454444</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.858043138153616</v>
+        <v>0.9127909155047456</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.261537166764753</v>
+        <v>4.294385833175431</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.533094278100318</v>
+        <v>-4.638025328348016</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926803716220146</v>
+        <v>1.884831296121067</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8700972650665788</v>
+        <v>0.9248450424177084</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.262456210813968</v>
+        <v>4.295304877224646</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574249397668539</v>
+        <v>-4.679180447916237</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912222298576994</v>
+        <v>1.870249878477915</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8289421454983579</v>
+        <v>0.8836899228494874</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.239643769257172</v>
+        <v>4.272492435667849</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.471368808139946</v>
+        <v>-4.576299858387644</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.966225560266313</v>
+        <v>1.924253140167234</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9318227350269508</v>
+        <v>0.9865705123780804</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.31422314885221</v>
+        <v>4.347071815262888</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.702969201309447</v>
+        <v>-4.807900251557145</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.893788073172107</v>
+        <v>1.851815653073028</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9318227350269508</v>
+        <v>0.9865705123780804</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.334425819025804</v>
+        <v>4.367274485436482</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721041709601058</v>
+        <v>-4.825972759848757</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886559069855463</v>
+        <v>1.844586649756383</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9318227350269508</v>
+        <v>0.9865705123780804</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.334425819025804</v>
+        <v>4.367274485436482</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.896148542177503</v>
+        <v>-5.001079592425201</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776768250418352</v>
+        <v>1.734795830319272</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9318227350269508</v>
+        <v>0.9865705123780804</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.294677732619271</v>
+        <v>4.327526399029948</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.864862521637048</v>
+        <v>-4.969793571884746</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.796305277631474</v>
+        <v>1.754332857532394</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9631087555674062</v>
+        <v>1.017856532918536</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.320471963940484</v>
+        <v>4.353320630351162</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.711837129523763</v>
+        <v>-4.816768179771461</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.956686434049692</v>
+        <v>1.914714013950613</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.11613414768069</v>
+        <v>1.17088192503182</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.511458198781359</v>
+        <v>4.544306865192037</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.740144443397034</v>
+        <v>-4.845075493644732</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132829733408676</v>
+        <v>2.090857313309597</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.11613414768069</v>
+        <v>1.17088192503182</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.698924423689651</v>
+        <v>4.731773090100329</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.906737668510556</v>
+        <v>-5.011668718758254</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.035595394717349</v>
+        <v>1.99362297461827</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9495409225671678</v>
+        <v>1.004288699918297</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.568371439975619</v>
+        <v>4.601220106386298</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.733673289128256</v>
+        <v>-4.838604339375954</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.108497549131987</v>
+        <v>2.066525129032907</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9495409225671678</v>
+        <v>1.004288699918297</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.572047842637337</v>
+        <v>4.604896509048015</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.704427308672559</v>
+        <v>-4.809358358920258</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.117813996437761</v>
+        <v>2.075841576338681</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9495409225671678</v>
+        <v>1.004288699918297</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.569665897760832</v>
+        <v>4.602514564171511</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.81135285655041</v>
+        <v>-4.916283906798109</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.072337016444255</v>
+        <v>2.030364596345176</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8426153746893165</v>
+        <v>0.8973631520404458</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.502803808191757</v>
+        <v>4.535652474602434</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.956371415057659</v>
+        <v>-5.061302465305357</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.01575839518459</v>
+        <v>1.973785975085511</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6975968161820679</v>
+        <v>0.7523445935331973</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.417221475230642</v>
+        <v>4.450070141641319</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.074713180842377</v>
+        <v>-5.179644231090075</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068352928128456</v>
+        <v>2.026380508029377</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.708282854744958</v>
+        <v>0.7630306320960873</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.523564337626129</v>
+        <v>4.556413004036806</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073536</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.126123603163085</v>
+        <v>-5.231054653410783</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.045574456326112</v>
+        <v>2.003602036227032</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.708282854744958</v>
+        <v>0.7630306320960873</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.521350034752068</v>
+        <v>4.554198701162745</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.205543054370836</v>
+        <v>-5.310474104618534</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.013709803917301</v>
+        <v>1.971737383818221</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.708282854744958</v>
+        <v>0.7630306320960873</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.521253162826357</v>
+        <v>4.554101829237035</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581132</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.301006052288054</v>
+        <v>-5.405937102535752</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.975518498308457</v>
+        <v>1.933546078209378</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.708282854744958</v>
+        <v>0.7630306320960873</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.521247056384401</v>
+        <v>4.554095722795078</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500734</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.278256820353828</v>
+        <v>-5.385435364923902</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.982714587644758</v>
+        <v>1.939843169816728</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.731032086679184</v>
+        <v>0.7835323697079373</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.532992992107547</v>
+        <v>4.564493161924799</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636269</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.333625982486022</v>
+        <v>-5.440804527056096</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.966300740539607</v>
+        <v>1.923429322711578</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.731032086679184</v>
+        <v>0.7835323697079373</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.538726809855274</v>
+        <v>4.570226979672526</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.379063762316849</v>
+        <v>-5.486242306886923</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.947663991950209</v>
+        <v>1.90479257412218</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6881870960010243</v>
+        <v>0.7406873790297777</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.512558178791311</v>
+        <v>4.544058348608563</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.295838305469185</v>
+        <v>-5.403016850039259</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.000828567539594</v>
+        <v>1.957957149711564</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6881870960010243</v>
+        <v>0.7406873790297777</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.53243257164163</v>
+        <v>4.563932741458882</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.119548080863877</v>
+        <v>-5.226726625433951</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.055045357906445</v>
+        <v>2.012173940078415</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6881870960010243</v>
+        <v>0.7406873790297777</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.516133272166358</v>
+        <v>4.54763344198361</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.936336417730782</v>
+        <v>-5.043514962300856</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.130760972623728</v>
+        <v>2.087889554795699</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6881870960010243</v>
+        <v>0.7406873790297777</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.518564221630403</v>
+        <v>4.550064391447656</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.864614970716931</v>
+        <v>-4.971793515287005</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.125240737277158</v>
+        <v>2.082369319449128</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.759908543014875</v>
+        <v>0.8124088260436283</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.527388275686603</v>
+        <v>4.558888445503855</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.993993753356709</v>
+        <v>-5.101172297926783</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.020404970142418</v>
+        <v>1.977533552314389</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7178067703076716</v>
+        <v>0.7703070533364249</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.449042957983453</v>
+        <v>4.480543127800704</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.027010049267454</v>
+        <v>-5.134188593837528</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.192396656663476</v>
+        <v>2.149525238835447</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6483693936409201</v>
+        <v>0.7008696766696734</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.592578736868758</v>
+        <v>4.624078906686009</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.015482413617845</v>
+        <v>-5.122660958187919</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.188928936751569</v>
+        <v>2.146057518923539</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7073700518422825</v>
+        <v>0.7598703348710358</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.619900357617824</v>
+        <v>4.651400527435076</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.112823914960214</v>
+        <v>-5.220002459530288</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.15366044873641</v>
+        <v>2.11078903090838</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6629498696767941</v>
+        <v>0.7154501527055475</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.59691636084032</v>
+        <v>4.628416530657571</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.815293335538338</v>
+        <v>3.713486896756334</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.364439701821476</v>
+        <v>4.317304136351363</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.112823914960214</v>
+        <v>-5.220002459530288</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.15366044873641</v>
+        <v>2.11078903090838</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6629498696767941</v>
+        <v>0.7154501527055475</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.357503498807843</v>
+        <v>4.310367933337731</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>110.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.6%</t>
+          <t>-685.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.1%</t>
+          <t>-165.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.1%</t>
+          <t>589.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.9%</t>
+          <t>-309.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-161.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-24.4%</t>
         </is>
       </c>
     </row>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.648318729253103</v>
+        <v>-3.649294579345426</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.916348105617068</v>
+        <v>1.915957765580139</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7878839615667601</v>
+        <v>0.7890367480840959</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848762398572113</v>
+        <v>3.849454070482514</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.676219516362576</v>
+        <v>-3.677195366454899</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.903711831900281</v>
+        <v>1.903321491863352</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7532870374238253</v>
+        <v>0.754439823941161</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.826528285213354</v>
+        <v>3.827219957123755</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.79874561906547</v>
+        <v>-3.799721469157793</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.851465834796322</v>
+        <v>1.851075494759393</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6307609347209314</v>
+        <v>0.6319137212382672</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.749777067568816</v>
+        <v>3.750468739479218</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.029260115251059</v>
+        <v>-4.030235965343381</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.82596599591259</v>
+        <v>1.825575655875661</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4002464385353427</v>
+        <v>0.4013992250526784</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.678174329447967</v>
+        <v>3.678866001358368</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.378005200475503</v>
+        <v>-4.378981050567825</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.82677968082466</v>
+        <v>1.826389340787731</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2914984846164449</v>
+        <v>0.2926512711337806</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.753237276098475</v>
+        <v>3.753928948008877</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.531991618251643</v>
+        <v>-4.532967468343966</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.834165382859843</v>
+        <v>1.833775042822914</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2914984846164449</v>
+        <v>0.2926512711337806</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.822217545244115</v>
+        <v>3.822909217154517</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.481469714423977</v>
+        <v>-4.4824455645163</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.840425346511031</v>
+        <v>1.840035006474102</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2914984846164449</v>
+        <v>0.2926512711337806</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.808268747364236</v>
+        <v>3.808960419274638</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.733944868431702</v>
+        <v>-4.734920718524024</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.751305773963355</v>
+        <v>1.750915433926426</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2914984846164449</v>
+        <v>0.2926512711337806</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.82013923641965</v>
+        <v>3.820830908330052</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.026840624911114</v>
+        <v>-5.027816475003436</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.635358005890533</v>
+        <v>1.634967665853605</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2914984846164449</v>
+        <v>0.2926512711337806</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.821349770938594</v>
+        <v>3.822041442848995</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.213504753045922</v>
+        <v>-5.214480603138244</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.564814096863932</v>
+        <v>1.564423756827003</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.264759513791885</v>
+        <v>0.2659123003092208</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.809428130671179</v>
+        <v>3.810119802581581</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.359525439959884</v>
+        <v>-5.360501290052206</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.501483674834536</v>
+        <v>1.501093334797607</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.255676421998028</v>
+        <v>0.2568292085153638</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.799056128331054</v>
+        <v>3.799747800241456</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.451239449069469</v>
+        <v>-5.452215299161791</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.627002127889746</v>
+        <v>1.626611787852818</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.255676421998028</v>
+        <v>0.2568292085153638</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.961260185030098</v>
+        <v>3.9619518569405</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.482891108129438</v>
+        <v>-5.483866958221761</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.609188102229573</v>
+        <v>1.608797762192644</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2505079647535878</v>
+        <v>0.2516607512709236</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.953005748647248</v>
+        <v>3.95369742055765</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.564825926398322</v>
+        <v>-5.565801776490644</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.586643592490511</v>
+        <v>1.586253252453582</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2405732191665076</v>
+        <v>0.2417260056838434</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.957274318863491</v>
+        <v>3.957965990773893</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.666802048646729</v>
+        <v>-5.667777898739051</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.55477878204705</v>
+        <v>1.554388442010121</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1385970969181001</v>
+        <v>0.1397498834354358</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.905014283970349</v>
+        <v>3.905705955880751</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.556795765169507</v>
+        <v>-5.55777161526183</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.590934182682114</v>
+        <v>1.590543842645185</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1618016688353753</v>
+        <v>0.162954455352711</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.91108991436489</v>
+        <v>3.911781586275292</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.458474222443379</v>
+        <v>-5.414712039520904</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.63451281049454</v>
+        <v>1.65201768366353</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1974199902319372</v>
+        <v>0.1709678819426903</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.936710917924802</v>
+        <v>3.920839652951253</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.157027496971542</v>
+        <v>-5.113265314049066</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.762352383565811</v>
+        <v>1.779857256734801</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4988667157037745</v>
+        <v>0.4724146074145276</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.12483983609044</v>
+        <v>4.108968571116892</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.181617741206725</v>
+        <v>-5.13785555828425</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.753487463624448</v>
+        <v>1.770992336793438</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4988667157037745</v>
+        <v>0.4724146074145276</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.12581101384315</v>
+        <v>4.109939748869603</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.130579365200205</v>
+        <v>-5.08681718227773</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.774745718406812</v>
+        <v>1.792250591575802</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4988667157037745</v>
+        <v>0.4724146074145276</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.126653918222906</v>
+        <v>4.110782653249358</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.089440070333574</v>
+        <v>-5.045677887411099</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.810239535227609</v>
+        <v>1.8277444083966</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5400060105704053</v>
+        <v>0.5135539022811584</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.17037559401703</v>
+        <v>4.154504329043482</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.992805158314934</v>
+        <v>-4.949042975392459</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.665077496159</v>
+        <v>1.68258236932799</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6366409225890453</v>
+        <v>0.6101888142997983</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.044540537352148</v>
+        <v>4.0286692723786</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.123385892845777</v>
+        <v>-5.079623709923301</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.616347246420627</v>
+        <v>1.633852119589617</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5060601880582027</v>
+        <v>0.4796080797689558</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.969694140707607</v>
+        <v>3.953822875734059</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.958889558654815</v>
+        <v>-4.915127375732339</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.666572599173094</v>
+        <v>1.684077472342085</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6705565222491646</v>
+        <v>0.6441044139599177</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.052818760298266</v>
+        <v>4.036947495324719</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.986259491339247</v>
+        <v>-4.942497308416772</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.654812336535751</v>
+        <v>1.672317209704741</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6705565222491646</v>
+        <v>0.6441044139599177</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.052006470734696</v>
+        <v>4.036135205761148</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.996644686229136</v>
+        <v>-4.952882503306661</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.660527037704868</v>
+        <v>1.678031910873858</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6601713273592753</v>
+        <v>0.6337192190700284</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.055644132925835</v>
+        <v>4.039772867952287</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.015232844951361</v>
+        <v>-4.971470662028886</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.723928779992403</v>
+        <v>1.741433653161393</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6415831686370499</v>
+        <v>0.6151310603478031</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.115328243468925</v>
+        <v>4.099456978495377</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.015531391647397</v>
+        <v>-4.971769208724922</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.720678372132287</v>
+        <v>1.738183245301277</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.641284621941014</v>
+        <v>0.6148325136517672</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.112018126269602</v>
+        <v>4.096146861296054</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.91470825795697</v>
+        <v>-4.870946075034494</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.76553852054785</v>
+        <v>1.78304339371684</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6537488374253678</v>
+        <v>0.627296729136121</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.124027550499606</v>
+        <v>4.108156285526058</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.723926897204562</v>
+        <v>-4.680164714282087</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.841980318327356</v>
+        <v>1.859485191496346</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8445301981777752</v>
+        <v>0.8180780898885284</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.238625620429594</v>
+        <v>4.222754355456045</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.705410043162741</v>
+        <v>-4.661647860240267</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.829223905681681</v>
+        <v>1.846728778850671</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8574603276029834</v>
+        <v>0.8310082193137366</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.226220543822315</v>
+        <v>4.210349278848767</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.650079455260979</v>
+        <v>-4.606317272338504</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.886323077454444</v>
+        <v>1.903827950623434</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9127909155047456</v>
+        <v>0.8863388072154987</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.294385833175431</v>
+        <v>4.278514568201882</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.638025328348016</v>
+        <v>-4.594263145425542</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.884831296121067</v>
+        <v>1.902336169290057</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9248450424177084</v>
+        <v>0.8983929341284616</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.295304877224646</v>
+        <v>4.279433612251098</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.679180447916237</v>
+        <v>-4.635418264993763</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.870249878477915</v>
+        <v>1.887754751646904</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8836899228494874</v>
+        <v>0.8572378145602406</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.272492435667849</v>
+        <v>4.256621170694301</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.576299858387644</v>
+        <v>-4.53253767546517</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.924253140167234</v>
+        <v>1.941758013336224</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9865705123780804</v>
+        <v>0.9601184040888335</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.347071815262888</v>
+        <v>4.331200550289339</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.807900251557145</v>
+        <v>-4.76413806863467</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.851815653073028</v>
+        <v>1.869320526242018</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9865705123780804</v>
+        <v>0.9601184040888335</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.367274485436482</v>
+        <v>4.351403220462934</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.825972759848757</v>
+        <v>-4.782210576926282</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.844586649756383</v>
+        <v>1.862091522925373</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9865705123780804</v>
+        <v>0.9601184040888335</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.367274485436482</v>
+        <v>4.351403220462934</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.001079592425201</v>
+        <v>-4.957317409502727</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.734795830319272</v>
+        <v>1.752300703488262</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9865705123780804</v>
+        <v>0.9601184040888335</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.327526399029948</v>
+        <v>4.311655134056401</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.969793571884746</v>
+        <v>-4.926031388962271</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.754332857532394</v>
+        <v>1.771837730701384</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.017856532918536</v>
+        <v>0.9914044246292888</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.353320630351162</v>
+        <v>4.337449365377614</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.816768179771461</v>
+        <v>-4.773005996848987</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.914714013950613</v>
+        <v>1.932218887119602</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.17088192503182</v>
+        <v>1.144429816742573</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.544306865192037</v>
+        <v>4.528435600218488</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.845075493644732</v>
+        <v>-4.801313310722257</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.090857313309597</v>
+        <v>2.108362186478586</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.17088192503182</v>
+        <v>1.144429816742573</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.731773090100329</v>
+        <v>4.715901825126781</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.011668718758254</v>
+        <v>-4.967906535835779</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.99362297461827</v>
+        <v>2.01112784778726</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.004288699918297</v>
+        <v>0.9778365916290503</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.601220106386298</v>
+        <v>4.585348841412749</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.838604339375954</v>
+        <v>-4.79484215645348</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.066525129032907</v>
+        <v>2.084030002201898</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.004288699918297</v>
+        <v>0.9778365916290503</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.604896509048015</v>
+        <v>4.589025244074467</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.809358358920258</v>
+        <v>-4.765596175997783</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.075841576338681</v>
+        <v>2.093346449507671</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.004288699918297</v>
+        <v>0.9778365916290503</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.602514564171511</v>
+        <v>4.586643299197962</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.916283906798109</v>
+        <v>-4.872521723875634</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.030364596345176</v>
+        <v>2.047869469514166</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8973631520404458</v>
+        <v>0.870911043751199</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.535652474602434</v>
+        <v>4.519781209628887</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.061302465305357</v>
+        <v>-5.017540282382883</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.973785975085511</v>
+        <v>1.991290848254501</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7523445935331973</v>
+        <v>0.7258924852439504</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.450070141641319</v>
+        <v>4.434198876667772</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.179644231090075</v>
+        <v>-5.1358820481676</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.026380508029377</v>
+        <v>2.043885381198367</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7630306320960873</v>
+        <v>0.7365785238068405</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.556413004036806</v>
+        <v>4.540541739063259</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.231054653410783</v>
+        <v>-5.187292470488308</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.003602036227032</v>
+        <v>2.021106909396022</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7630306320960873</v>
+        <v>0.7365785238068405</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.554198701162745</v>
+        <v>4.538327436189197</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.310474104618534</v>
+        <v>-5.26671192169606</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.971737383818221</v>
+        <v>1.989242256987211</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7630306320960873</v>
+        <v>0.7365785238068405</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.554101829237035</v>
+        <v>4.538230564263487</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581132</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.405937102535752</v>
+        <v>-5.362174919613278</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.933546078209378</v>
+        <v>1.951050951378368</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7630306320960873</v>
+        <v>0.7365785238068405</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.554095722795078</v>
+        <v>4.53822445782153</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500734</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.385435364923902</v>
+        <v>-5.402194917657061</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.939843169816728</v>
+        <v>1.933139348723464</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7835323697079373</v>
+        <v>0.6965585257630567</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.564493161924799</v>
+        <v>4.512308855557871</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636269</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.440804527056096</v>
+        <v>-5.457564079789255</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.923429322711578</v>
+        <v>1.916725501618314</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7835323697079373</v>
+        <v>0.6965585257630567</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.570226979672526</v>
+        <v>4.518042673305597</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.486242306886923</v>
+        <v>-5.503001859620082</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.90479257412218</v>
+        <v>1.898088753028916</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7406873790297777</v>
+        <v>0.653713535084897</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.544058348608563</v>
+        <v>4.491874042241634</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.403016850039259</v>
+        <v>-5.419776402772418</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.957957149711564</v>
+        <v>1.9512533286183</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7406873790297777</v>
+        <v>0.653713535084897</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.563932741458882</v>
+        <v>4.511748435091953</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.226726625433951</v>
+        <v>-5.24348617816711</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.012173940078415</v>
+        <v>2.005470118985151</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7406873790297777</v>
+        <v>0.653713535084897</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.54763344198361</v>
+        <v>4.495449135616681</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.043514962300856</v>
+        <v>-5.060274515034015</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.087889554795699</v>
+        <v>2.081185733702435</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7406873790297777</v>
+        <v>0.653713535084897</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.550064391447656</v>
+        <v>4.497880085080727</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.971793515287005</v>
+        <v>-4.988553068020164</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.082369319449128</v>
+        <v>2.075665498355865</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8124088260436283</v>
+        <v>0.7254349820987477</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.558888445503855</v>
+        <v>4.506704139136927</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.101172297926783</v>
+        <v>-5.117931850659942</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.977533552314389</v>
+        <v>1.970829731221125</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7703070533364249</v>
+        <v>0.6833332093915443</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.480543127800704</v>
+        <v>4.428358821433776</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.134188593837528</v>
+        <v>-5.150948146570687</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.149525238835447</v>
+        <v>2.142821417742183</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7008696766696734</v>
+        <v>0.6138958327247928</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.624078906686009</v>
+        <v>4.571894600319081</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.122660958187919</v>
+        <v>-5.139420510921078</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.146057518923539</v>
+        <v>2.139353697830276</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7598703348710358</v>
+        <v>0.6728964909261552</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.651400527435076</v>
+        <v>4.599216221068147</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.71717088451903</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.220002459530288</v>
+        <v>-5.236762012263447</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.11078903090838</v>
+        <v>2.104085209815116</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7154501527055475</v>
+        <v>0.6284763087606668</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.628416530657571</v>
+        <v>4.576232224290643</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.713486896756334</v>
+        <v>3.713486896756332</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.317304136351363</v>
+        <v>4.223080255515912</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.220002459530288</v>
+        <v>-5.236762012263447</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.11078903090838</v>
+        <v>2.104085209815116</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7154501527055475</v>
+        <v>0.6284763087606668</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.310367933337731</v>
+        <v>4.21614405250228</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>108.4%</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.2%</t>
+          <t>-687.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.8%</t>
+          <t>-166.6%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.71717088451903</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.713486896756332</v>
+        <v>3.713486896756334</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.223080255515912</v>
+        <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.236762012263447</v>
+        <v>-5.25954022200852</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.104085209815116</v>
+        <v>2.096225008109925</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6284763087606668</v>
+        <v>0.6286896423559739</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.21614405250228</v>
+        <v>4.577611306640665</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240831.xlsx
+++ b/tame_output/ON/bt/strategyON_20240831.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.4%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.5%</t>
+          <t>-677.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.6%</t>
+          <t>-162.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.9%</t>
+          <t>590.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.4%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.1%</t>
+          <t>-159.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.649294579345426</v>
+        <v>-3.676715012510379</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.915957765580139</v>
+        <v>1.904989592314158</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7890367480840959</v>
+        <v>0.7607410790222131</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.849454070482514</v>
+        <v>3.832476669045385</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.677195366454899</v>
+        <v>-3.704615799619852</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.903321491863352</v>
+        <v>1.892353318597371</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.754439823941161</v>
+        <v>0.7261441548792783</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.827219957123755</v>
+        <v>3.810242555686626</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.799721469157793</v>
+        <v>-3.827141902322746</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.851075494759393</v>
+        <v>1.840107321493412</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6319137212382672</v>
+        <v>0.6036180521763844</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.750468739479218</v>
+        <v>3.733491338042088</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.030235965343381</v>
+        <v>-4.057656398508334</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.825575655875661</v>
+        <v>1.81460748260968</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4013992250526784</v>
+        <v>0.3731035559907957</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.678866001358368</v>
+        <v>3.661888599921239</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.378981050567825</v>
+        <v>-4.406401483732778</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.826389340787731</v>
+        <v>1.81542116752175</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2926512711337806</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.753928948008877</v>
+        <v>3.736951546571747</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.532967468343966</v>
+        <v>-4.560387901508919</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.833775042822914</v>
+        <v>1.822806869556933</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2926512711337806</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.822909217154517</v>
+        <v>3.805931815717387</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.4824455645163</v>
+        <v>-4.509865997681253</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.840035006474102</v>
+        <v>1.82906683320812</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2926512711337806</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.808960419274638</v>
+        <v>3.791983017837508</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.734920718524024</v>
+        <v>-4.762341151688977</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.750915433926426</v>
+        <v>1.739947260660445</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2926512711337806</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.820830908330052</v>
+        <v>3.803853506892922</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.027816475003436</v>
+        <v>-5.055236908168389</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.634967665853605</v>
+        <v>1.623999492587624</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2926512711337806</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.822041442848995</v>
+        <v>3.805064041411865</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.214480603138244</v>
+        <v>-5.241901036303197</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.564423756827003</v>
+        <v>1.553455583561022</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2659123003092208</v>
+        <v>0.237616631247338</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.810119802581581</v>
+        <v>3.793142401144451</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.360501290052206</v>
+        <v>-5.387921723217159</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.501093334797607</v>
+        <v>1.490125161531626</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2568292085153638</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.799747800241456</v>
+        <v>3.782770398804326</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.452215299161791</v>
+        <v>-5.479635732326745</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.626611787852818</v>
+        <v>1.615643614586836</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2568292085153638</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.9619518569405</v>
+        <v>3.94497445550337</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.483866958221761</v>
+        <v>-5.511287391386714</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.608797762192644</v>
+        <v>1.597829588926662</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2516607512709236</v>
+        <v>0.2233650822090408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.95369742055765</v>
+        <v>3.93672001912052</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.565801776490644</v>
+        <v>-5.593222209655598</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.586253252453582</v>
+        <v>1.575285079187601</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2417260056838434</v>
+        <v>0.2134303366219606</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.957965990773893</v>
+        <v>3.940988589336763</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.667777898739051</v>
+        <v>-5.695198331904005</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.554388442010121</v>
+        <v>1.54342026874414</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1397498834354358</v>
+        <v>0.1114542143735531</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.905705955880751</v>
+        <v>3.888728554443621</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.55777161526183</v>
+        <v>-5.585192048426784</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.590543842645185</v>
+        <v>1.579575669379204</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.162954455352711</v>
+        <v>0.1346587862908283</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.911781586275292</v>
+        <v>3.894804184838162</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.414712039520904</v>
+        <v>-5.442132472685858</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.65201768366353</v>
+        <v>1.641049510397548</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1709678819426903</v>
+        <v>0.1426722128808076</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.920839652951253</v>
+        <v>3.903862251514123</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.113265314049066</v>
+        <v>-5.14068574721402</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.779857256734801</v>
+        <v>1.76888908346882</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4724146074145276</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.108968571116892</v>
+        <v>4.091991169679762</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.13785555828425</v>
+        <v>-5.165275991449204</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.770992336793438</v>
+        <v>1.760024163527456</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4724146074145276</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.109939748869603</v>
+        <v>4.092962347432472</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.08681718227773</v>
+        <v>-5.114237615442684</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.792250591575802</v>
+        <v>1.78128241830982</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4724146074145276</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.110782653249358</v>
+        <v>4.093805251812228</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.045677887411099</v>
+        <v>-5.073098320576053</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.8277444083966</v>
+        <v>1.816776235130618</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5135539022811584</v>
+        <v>0.4852582332192756</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.154504329043482</v>
+        <v>4.137526927606352</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.949042975392459</v>
+        <v>-4.976463408557413</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.68258236932799</v>
+        <v>1.671614196062009</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6101888142997983</v>
+        <v>0.5818931452379156</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.0286692723786</v>
+        <v>4.011691870941471</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.079623709923301</v>
+        <v>-5.107044143088255</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.633852119589617</v>
+        <v>1.622883946323636</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4796080797689558</v>
+        <v>0.4513124107070731</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.953822875734059</v>
+        <v>3.936845474296929</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.915127375732339</v>
+        <v>-4.942547808897293</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.684077472342085</v>
+        <v>1.673109299076103</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6441044139599177</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.036947495324719</v>
+        <v>4.019970093887589</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.942497308416772</v>
+        <v>-4.969917741581726</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.672317209704741</v>
+        <v>1.66134903643876</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6441044139599177</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.036135205761148</v>
+        <v>4.019157804324019</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.952882503306661</v>
+        <v>-4.980302936471615</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.678031910873858</v>
+        <v>1.667063737607877</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6337192190700284</v>
+        <v>0.6054235500081456</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.039772867952287</v>
+        <v>4.022795466515158</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.971470662028886</v>
+        <v>-4.99889109519384</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.741433653161393</v>
+        <v>1.730465479895412</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6151310603478031</v>
+        <v>0.5868353912859203</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.099456978495377</v>
+        <v>4.082479577058248</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.971769208724922</v>
+        <v>-4.999189641889876</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.738183245301277</v>
+        <v>1.727215072035296</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6148325136517672</v>
+        <v>0.5865368445898844</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.096146861296054</v>
+        <v>4.079169459858925</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.870946075034494</v>
+        <v>-4.898366508199448</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.78304339371684</v>
+        <v>1.772075220450858</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.627296729136121</v>
+        <v>0.5990010600742383</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.108156285526058</v>
+        <v>4.091178884088928</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.680164714282087</v>
+        <v>-4.707585147447041</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.859485191496346</v>
+        <v>1.848517018230365</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8180780898885284</v>
+        <v>0.7897824208266456</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.222754355456045</v>
+        <v>4.205776954018916</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.661647860240267</v>
+        <v>-4.599043985630608</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.846728778850671</v>
+        <v>1.871770328694534</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8310082193137366</v>
+        <v>0.8483279070786934</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.210349278848767</v>
+        <v>4.220741091507741</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.606317272338504</v>
+        <v>-4.543713397728846</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.903827950623434</v>
+        <v>1.928869500467298</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8863388072154987</v>
+        <v>0.9036584949804556</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.278514568201882</v>
+        <v>4.288906380860857</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.594263145425542</v>
+        <v>-4.531659270815883</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.902336169290057</v>
+        <v>1.92737771913392</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8983929341284616</v>
+        <v>0.9157126218934184</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.279433612251098</v>
+        <v>4.289825424910072</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.635418264993763</v>
+        <v>-4.572814390384104</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.887754751646904</v>
+        <v>1.912796301490768</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8572378145602406</v>
+        <v>0.8745575023251975</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.256621170694301</v>
+        <v>4.267012983353276</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.53253767546517</v>
+        <v>-4.469933800855511</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.941758013336224</v>
+        <v>1.966799563180087</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9601184040888335</v>
+        <v>0.9774380918537904</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.331200550289339</v>
+        <v>4.341592362948314</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.76413806863467</v>
+        <v>-4.701534194025012</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.869320526242018</v>
+        <v>1.894362076085881</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9601184040888335</v>
+        <v>0.9774380918537904</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.351403220462934</v>
+        <v>4.361795033121908</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.782210576926282</v>
+        <v>-4.719606702316623</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.862091522925373</v>
+        <v>1.887133072769237</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9601184040888335</v>
+        <v>0.9774380918537904</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.351403220462934</v>
+        <v>4.361795033121908</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.957317409502727</v>
+        <v>-4.894713534893068</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.752300703488262</v>
+        <v>1.777342253332125</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9601184040888335</v>
+        <v>0.9774380918537904</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.311655134056401</v>
+        <v>4.322046946715375</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.926031388962271</v>
+        <v>-4.863427514352613</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.771837730701384</v>
+        <v>1.796879280545248</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9914044246292888</v>
+        <v>1.008724112394246</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.337449365377614</v>
+        <v>4.347841178036588</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.773005996848987</v>
+        <v>-4.710402122239328</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.932218887119602</v>
+        <v>1.957260436963466</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.144429816742573</v>
+        <v>1.16174950450753</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.528435600218488</v>
+        <v>4.538827412877462</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.801313310722257</v>
+        <v>-4.738709436112599</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.108362186478586</v>
+        <v>2.13340373632245</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.144429816742573</v>
+        <v>1.16174950450753</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.715901825126781</v>
+        <v>4.726293637785755</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.967906535835779</v>
+        <v>-4.905302661226121</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.01112784778726</v>
+        <v>2.036169397631123</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9778365916290503</v>
+        <v>0.9951562793940074</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.585348841412749</v>
+        <v>4.595740654071723</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.79484215645348</v>
+        <v>-4.732238281843821</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.084030002201898</v>
+        <v>2.109071552045761</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9778365916290503</v>
+        <v>0.9951562793940074</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.589025244074467</v>
+        <v>4.599417056733441</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.765596175997783</v>
+        <v>-4.702992301388124</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.093346449507671</v>
+        <v>2.118387999351535</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9778365916290503</v>
+        <v>0.9951562793940074</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.586643299197962</v>
+        <v>4.597035111856936</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.872521723875634</v>
+        <v>-4.809917849265975</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.047869469514166</v>
+        <v>2.072911019358029</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.870911043751199</v>
+        <v>0.8882307315161561</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.519781209628887</v>
+        <v>4.530173022287861</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.017540282382883</v>
+        <v>-4.954936407773224</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.991290848254501</v>
+        <v>2.016332398098364</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7258924852439504</v>
+        <v>0.7432121730089075</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.434198876667772</v>
+        <v>4.444590689326746</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.1358820481676</v>
+        <v>-5.073278173557942</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.043885381198367</v>
+        <v>2.06892693104223</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7365785238068405</v>
+        <v>0.7538982115717976</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.540541739063259</v>
+        <v>4.550933551722233</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.187292470488308</v>
+        <v>-5.124688595878649</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.021106909396022</v>
+        <v>2.046148459239886</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7365785238068405</v>
+        <v>0.7538982115717976</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.538327436189197</v>
+        <v>4.548719248848172</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.26671192169606</v>
+        <v>-5.204108047086401</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.989242256987211</v>
+        <v>2.014283806831075</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7365785238068405</v>
+        <v>0.7538982115717976</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.538230564263487</v>
+        <v>4.548622376922461</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.362174919613278</v>
+        <v>-5.299571045003619</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.951050951378368</v>
+        <v>1.976092501222231</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7365785238068405</v>
+        <v>0.7538982115717976</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.53822445782153</v>
+        <v>4.548616270480505</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.402194917657061</v>
+        <v>-5.339591043047403</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.933139348723464</v>
+        <v>1.958180898567328</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6965585257630567</v>
+        <v>0.7138782135280137</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.512308855557871</v>
+        <v>4.522700668216845</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.457564079789255</v>
+        <v>-5.285261551324832</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.916725501618314</v>
+        <v>1.985646513004083</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6965585257630567</v>
+        <v>0.7138782135280137</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.518042673305597</v>
+        <v>4.528434485964572</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.503001859620082</v>
+        <v>-5.330699331155659</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.898088753028916</v>
+        <v>1.967009764414685</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.653713535084897</v>
+        <v>0.6710332228498541</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.491874042241634</v>
+        <v>4.502265854900608</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.419776402772418</v>
+        <v>-5.247473874307995</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.9512533286183</v>
+        <v>2.02017434000407</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.653713535084897</v>
+        <v>0.6710332228498541</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.511748435091953</v>
+        <v>4.522140247750928</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.24348617816711</v>
+        <v>-5.071183649702688</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.005470118985151</v>
+        <v>2.074391130370921</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.653713535084897</v>
+        <v>0.6710332228498541</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.495449135616681</v>
+        <v>4.505840948275655</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.060274515034015</v>
+        <v>-4.887971986569593</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.081185733702435</v>
+        <v>2.150106745088204</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.653713535084897</v>
+        <v>0.6710332228498541</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.497880085080727</v>
+        <v>4.508271897739701</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.988553068020164</v>
+        <v>-4.816250539555742</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.075665498355865</v>
+        <v>2.144586509741634</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7254349820987477</v>
+        <v>0.7427546698637048</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.506704139136927</v>
+        <v>4.517095951795901</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.117931850659942</v>
+        <v>-4.945629322195519</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.970829731221125</v>
+        <v>2.039750742606894</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6833332093915443</v>
+        <v>0.7006528971565014</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.428358821433776</v>
+        <v>4.438750634092751</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.150948146570687</v>
+        <v>-4.978645618106264</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.142821417742183</v>
+        <v>2.211742429127952</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6138958327247928</v>
+        <v>0.6312155204897498</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.571894600319081</v>
+        <v>4.582286412978055</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.139420510921078</v>
+        <v>-4.967117982456656</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.139353697830276</v>
+        <v>2.208274709216044</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6728964909261552</v>
+        <v>0.6902161786911123</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.599216221068147</v>
+        <v>4.609608033727121</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519031</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.236762012263447</v>
+        <v>-5.064459483799024</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.104085209815116</v>
+        <v>2.173006221200886</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6284763087606668</v>
+        <v>0.6457959965256239</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.576232224290643</v>
+        <v>4.586624036949617</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.713486896756334</v>
+        <v>3.808270274865568</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.25954022200852</v>
+        <v>-5.161016593174588</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.096225008109925</v>
+        <v>2.135634459643498</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6286896423559739</v>
+        <v>0.6457959965256239</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.577611306640665</v>
+        <v>4.587875119142455</v>
       </c>
     </row>
   </sheetData>
